--- a/web/public/forms/orig/o-anjeon-pumjil-bi.xlsx
+++ b/web/public/forms/orig/o-anjeon-pumjil-bi.xlsx
@@ -898,7 +898,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="G1" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="G1" s="73" t="inlineStr">
@@ -1074,7 +1074,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="G1" s="73" t="inlineStr">
@@ -1683,7 +1683,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="G1" s="73" t="inlineStr">
@@ -2370,7 +2370,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="G1" s="73" t="inlineStr">
@@ -3536,7 +3536,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="G1" s="73" t="inlineStr">
@@ -3624,7 +3624,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="G1" s="73" t="inlineStr">
@@ -4236,7 +4236,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="G1" s="73" t="inlineStr">
@@ -4935,7 +4935,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="G1" s="73" t="inlineStr">
@@ -6117,7 +6117,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="T1" s="73" t="inlineStr">
@@ -8100,7 +8100,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="G1" s="2" t="inlineStr">
@@ -8664,7 +8664,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="G1" s="2" t="inlineStr">
@@ -9262,7 +9262,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="G1" s="2" t="inlineStr">
@@ -10427,7 +10427,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="G1" s="2" t="inlineStr">
@@ -10514,7 +10514,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="G1" s="2" t="inlineStr">
@@ -11109,7 +11109,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="G1" s="2" t="inlineStr">
@@ -11707,7 +11707,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="G1" s="2" t="inlineStr">
@@ -12888,7 +12888,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="T1" s="2" t="inlineStr">

--- a/web/public/forms/orig/o-anjeon-pumjil-bi.xlsx
+++ b/web/public/forms/orig/o-anjeon-pumjil-bi.xlsx
@@ -869,7 +869,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
         </is>
       </c>
       <c r="G1" s="2" t="inlineStr">
@@ -948,7 +948,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
         </is>
       </c>
       <c r="G1" s="2" t="inlineStr">
@@ -1438,7 +1438,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
         </is>
       </c>
       <c r="G1" s="2" t="inlineStr">
@@ -1957,7 +1957,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
         </is>
       </c>
       <c r="G1" s="2" t="inlineStr">
@@ -3123,7 +3123,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
         </is>
       </c>
       <c r="G1" s="2" t="inlineStr">
@@ -3202,7 +3202,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
         </is>
       </c>
       <c r="G1" s="2" t="inlineStr">
@@ -3699,7 +3699,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
         </is>
       </c>
       <c r="G1" s="2" t="inlineStr">
@@ -4218,7 +4218,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
         </is>
       </c>
       <c r="G1" s="2" t="inlineStr">
@@ -5400,7 +5400,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
         </is>
       </c>
       <c r="T1" s="2" t="inlineStr">
